--- a/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA BENGALA.xlsx
@@ -28,58 +28,58 @@
     <t>7899641895082</t>
   </si>
   <si>
-    <t>BUCHA BENG VEDAMOTOS CROSSER XTZ125 2003 A 2016</t>
+    <t>BUCHA BENGALA VEDAMOTOS CROSSER XTZ125 2003 A 2016</t>
   </si>
   <si>
     <t>7899641845377</t>
   </si>
   <si>
-    <t>BUCHA BENG VEDAMOTOS TORNADO XR250 2002 A 2008/ XRE300</t>
+    <t>BUCHA BENGALA VEDAMOTOS TORNADO XR250 2002 A 2008/ XRE300</t>
   </si>
   <si>
     <t>7899641895068</t>
   </si>
   <si>
-    <t>BUCHA BENG VEDAMOTOS LANDER XTZ250 2007 A 2015</t>
+    <t>BUCHA BENGALA VEDAMOTOS LANDER XTZ250 2007 A 2015</t>
   </si>
   <si>
     <t>7908073720272</t>
   </si>
   <si>
-    <t>BUCHA BENG SMARTFOX XRE300 TORNADO XR250 FALCON400 2008/ CB600 2010</t>
+    <t>BUCHA BENGALA SMARTFOX XRE300/ TORNADO XR250/ FALCON400 2008/ CB600 2010</t>
   </si>
   <si>
     <t>7893596253362</t>
   </si>
   <si>
-    <t>BUCHA BENG (PAR) MOTOBOR+ FAN CG TITAN150-160/ BROS NXR125-150-160</t>
+    <t>BUCHA BENGALA (PAR) MOTOPOR+ FAN CG TITAN150-160/ BROS NXR125-150-160</t>
   </si>
   <si>
     <t>7908073720258</t>
   </si>
   <si>
-    <t>BUCHA BENG SMARTFOX XR250 TORNADO</t>
+    <t>BUCHA BENGALA SMARTFOX XR250 TORNADO</t>
   </si>
   <si>
     <t>7908073720241</t>
   </si>
   <si>
-    <t>BUCHA BENG SMARTFOX FALCON400/ CB600</t>
+    <t>BUCHA BENGALA SMARTFOX FALCON400/ CB600</t>
   </si>
   <si>
-    <t>BUCHA BENG IRON CG TITAN150-160/ BROS NXR125 197587</t>
+    <t>BUCHA BENGALA IRON CG TITAN150-160/ BROS NXR125 197587</t>
   </si>
   <si>
     <t>7908305601942</t>
   </si>
   <si>
-    <t>BUCHA BENG TRILHA TITAN150 2004 A 2015/ BROS NXR150 2003 A 2014/ NXR160 2015 A 2022/ XRE190 2015 A 2016</t>
+    <t>BUCHA BENGALA TRILHA TITAN150 2004 A 2015/ BROS NXR150 2003 A 2014/ NXR160 2015 A 2022/ XRE190 2015 A 2016</t>
   </si>
   <si>
     <t>618341658349</t>
   </si>
   <si>
-    <t>BUCHA BENG IRON CB300R 2009 A 2015/ CB500 1997 A 2005/ CRF250F 2007 A 2019 197586</t>
+    <t>BUCHA BENGALA IRON CB300R 2009 A 2015/ CB500 1997 A 2005/ CRF250F 2007 A 2019 197586</t>
   </si>
 </sst>
 </file>
@@ -137,10 +137,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -410,10 +410,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>55.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -444,10 +446,12 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>1.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>90.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -478,10 +482,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>70.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -509,13 +515,15 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
         <v>6.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="4">
+        <v>35.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -543,13 +551,15 @@
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7">
         <v>5.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -577,7 +587,7 @@
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7">
@@ -613,13 +623,15 @@
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="7">
         <v>5.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="4">
+        <v>40.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -645,13 +657,15 @@
     </row>
     <row r="9">
       <c r="A9" s="8"/>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="7">
         <v>4.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -679,13 +693,15 @@
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="7">
         <v>2.0</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -713,7 +729,7 @@
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="7">
